--- a/files/Dashboards_Website.xlsx
+++ b/files/Dashboards_Website.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jschneid\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{219BCE34-4FD2-4B73-8069-C43FF485474F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BB83F33-B2CB-45F6-B420-925B9159067F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="380" windowWidth="19200" windowHeight="10010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="394">
   <si>
     <t>NAME</t>
   </si>
@@ -978,9 +978,6 @@
     <t>UNIL Open Access barometer</t>
   </si>
   <si>
-    <t>https://www.unil.ch/unil/en/home/menuinst/recherche/open-science/open-access/barometre-open-access-unil.html</t>
-  </si>
-  <si>
     <t>Université de Lausanne</t>
   </si>
   <si>
@@ -1132,6 +1129,99 @@
   </si>
   <si>
     <t>SWE</t>
+  </si>
+  <si>
+    <t>https://osm.nii.ac.jp/</t>
+  </si>
+  <si>
+    <t>Japan Open Science Monitor</t>
+  </si>
+  <si>
+    <t>2018–2025</t>
+  </si>
+  <si>
+    <t>The Research Center for Open Science and Data Platform (RCOS), National Institute of Informatics (NII)</t>
+  </si>
+  <si>
+    <t>https://ror.org/04ksd4g47</t>
+  </si>
+  <si>
+    <t>https://www.unil.ch/unil/en/home/menuinst/recherche/open-science/open-access/cadre-strategique-et-institutionnel/barometre-open-access-unil.html</t>
+  </si>
+  <si>
+    <t>https://anr.fr/en/anrs-role-in-research/commitments/open-science/the-anr-open-science-monitor/</t>
+  </si>
+  <si>
+    <t>ANR Open Science Monitor</t>
+  </si>
+  <si>
+    <t>2016–2024</t>
+  </si>
+  <si>
+    <t>Agence Nationale de la Recherche (ANR)</t>
+  </si>
+  <si>
+    <t>https://ror.org/00rbzpz17</t>
+  </si>
+  <si>
+    <t>https://www.couperin.org/so/depenses-apc/recueil-et-analyse-des-depenses-de-publication/</t>
+  </si>
+  <si>
+    <t>Couperin</t>
+  </si>
+  <si>
+    <t>https://ror.org/035c9qf67</t>
+  </si>
+  <si>
+    <t>Enquête APC</t>
+  </si>
+  <si>
+    <t>OpenAIRE Monitor Dashboard: Vrije Universiteit Amsterdam</t>
+  </si>
+  <si>
+    <t>https://monitor.openaire.eu/dashboard/vu</t>
+  </si>
+  <si>
+    <t>Vrije Universiteit Amsterdam</t>
+  </si>
+  <si>
+    <t>https://ror.org/008xxew50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLOS Open Science Indicators dashboard </t>
+  </si>
+  <si>
+    <t>https://lookerstudio.google.com/reporting/2b34c431-c3dd-4eed-ac69-0c8856bd8af7/page/GAiiF?utm_campaign=35281527-OSI-Dashboard&amp;utm_source=hubspot&amp;utm_medium=cta&amp;utm_content=explore-the-dashboard&amp;hsCtaAttrib=208961770045</t>
+  </si>
+  <si>
+    <t>2018–2024</t>
+  </si>
+  <si>
+    <t>Public Library of Science (PLOS)</t>
+  </si>
+  <si>
+    <t>https://ror.org/008zgvp64</t>
+  </si>
+  <si>
+    <t>https://plos.figshare.com/articles/dataset/PLOS_Open_Science_Indicators/21687686</t>
+  </si>
+  <si>
+    <t>https://metadata.datacite.org/</t>
+  </si>
+  <si>
+    <t>2016–2026</t>
+  </si>
+  <si>
+    <t>DataCite</t>
+  </si>
+  <si>
+    <t>https://ror.org/04wxnsj81</t>
+  </si>
+  <si>
+    <t>DataCite Metadata Dashboard</t>
+  </si>
+  <si>
+    <t>https://support.datacite.org/docs/datacite-metadata-dashboard</t>
   </si>
 </sst>
 </file>
@@ -1560,7 +1650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N89"/>
+  <dimension ref="A1:N95"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.33203125" style="2" customWidth="1"/>
@@ -1844,34 +1934,34 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>7</v>
+        <v>382</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>8</v>
+        <v>383</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>91</v>
+        <v>384</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>385</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>92</v>
+        <v>386</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>52</v>
+        <v>150</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>40</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>264</v>
+        <v>147</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>265</v>
@@ -1880,74 +1970,74 @@
         <v>131</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="N7" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="N7" s="2" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>253</v>
+        <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>134</v>
+        <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>258</v>
+        <v>284</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>132</v>
+        <v>91</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>40</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>56</v>
+        <v>151</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>147</v>
+        <v>265</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>290</v>
+        <v>131</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="N8" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="N8" s="4" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>6</v>
+        <v>253</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>147</v>
+        <v>133</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>132</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>150</v>
+        <v>53</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>40</v>
@@ -1959,16 +2049,16 @@
         <v>56</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>147</v>
+        <v>268</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>147</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>147</v>
+        <v>290</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>147</v>
+        <v>273</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>147</v>
@@ -1976,16 +2066,16 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>37</v>
+        <v>6</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>147</v>
@@ -2003,7 +2093,7 @@
         <v>56</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>266</v>
+        <v>147</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>147</v>
@@ -2012,7 +2102,7 @@
         <v>147</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>274</v>
+        <v>147</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>147</v>
@@ -2020,43 +2110,43 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>58</v>
+        <v>36</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>147</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>53</v>
+        <v>150</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>40</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>153</v>
+        <v>56</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>147</v>
+        <v>266</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>265</v>
+        <v>147</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>301</v>
+        <v>274</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>147</v>
@@ -2064,19 +2154,19 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>94</v>
+        <v>79</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>53</v>
@@ -2088,10 +2178,10 @@
         <v>10</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>265</v>
+        <v>147</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>265</v>
@@ -2100,7 +2190,7 @@
         <v>131</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>147</v>
@@ -2108,22 +2198,22 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>159</v>
+        <v>61</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>324</v>
+        <v>262</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>147</v>
+        <v>93</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>40</v>
@@ -2132,7 +2222,7 @@
         <v>10</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>153</v>
+        <v>129</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>265</v>
@@ -2147,21 +2237,21 @@
         <v>275</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>254</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>147</v>
@@ -2196,31 +2286,31 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>62</v>
+        <v>165</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>64</v>
+        <v>166</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>81</v>
+        <v>323</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>40</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>265</v>
@@ -2240,31 +2330,31 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>169</v>
+        <v>62</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>168</v>
+        <v>64</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>174</v>
+        <v>323</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>175</v>
+        <v>81</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>40</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>265</v>
@@ -2284,31 +2374,31 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>147</v>
+        <v>174</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>175</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>40</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>265</v>
@@ -2328,22 +2418,22 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>324</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>40</v>
@@ -2352,7 +2442,7 @@
         <v>2</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>265</v>
@@ -2372,87 +2462,87 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>331</v>
+        <v>176</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>332</v>
+        <v>177</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>147</v>
+        <v>178</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>179</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>40</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>335</v>
+        <v>137</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>147</v>
+        <v>265</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>147</v>
+        <v>265</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>336</v>
+        <v>275</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>147</v>
+        <v>254</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>14</v>
+        <v>330</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>331</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>96</v>
+        <v>333</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>53</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>152</v>
+        <v>334</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>267</v>
+        <v>147</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>277</v>
+        <v>147</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>278</v>
+        <v>335</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>147</v>
@@ -2460,43 +2550,43 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>17</v>
+        <v>392</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>388</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>97</v>
+        <v>389</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>390</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>98</v>
+        <v>391</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>52</v>
+        <v>150</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>56</v>
+        <v>153</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>147</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>290</v>
+        <v>131</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>279</v>
+        <v>393</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>147</v>
@@ -2504,19 +2594,19 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>305</v>
+        <v>325</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>53</v>
@@ -2525,22 +2615,22 @@
         <v>15</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>323</v>
+        <v>152</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>147</v>
+        <v>267</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N22" s="2" t="s">
         <v>147</v>
@@ -2548,19 +2638,19 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>20</v>
+        <v>370</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>21</v>
+        <v>369</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="D23" t="s">
-        <v>101</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>102</v>
+        <v>371</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>373</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>53</v>
@@ -2569,22 +2659,22 @@
         <v>15</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>56</v>
+        <v>137</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>147</v>
+        <v>267</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>147</v>
+        <v>277</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>290</v>
+        <v>131</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>287</v>
+        <v>147</v>
       </c>
       <c r="N23" s="2" t="s">
         <v>147</v>
@@ -2592,43 +2682,43 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>105</v>
+        <v>280</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>156</v>
+        <v>56</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>147</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>147</v>
+        <v>270</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>147</v>
+        <v>290</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="N24" s="2" t="s">
         <v>147</v>
@@ -2636,19 +2726,19 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>138</v>
+        <v>18</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>260</v>
+        <v>305</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>100</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>53</v>
@@ -2657,22 +2747,22 @@
         <v>15</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>56</v>
+        <v>322</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>147</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>147</v>
+        <v>265</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>147</v>
+        <v>276</v>
       </c>
       <c r="N25" s="2" t="s">
         <v>147</v>
@@ -2680,19 +2770,19 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>68</v>
+        <v>20</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>107</v>
+        <v>262</v>
+      </c>
+      <c r="D26" t="s">
+        <v>101</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>102</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>53</v>
@@ -2701,10 +2791,10 @@
         <v>15</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>151</v>
+        <v>56</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>147</v>
@@ -2713,10 +2803,10 @@
         <v>147</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>147</v>
+        <v>290</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>147</v>
+        <v>287</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>147</v>
@@ -2724,19 +2814,19 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>54</v>
+        <v>22</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>128</v>
+        <v>105</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>53</v>
@@ -2745,22 +2835,22 @@
         <v>15</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>56</v>
+        <v>156</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>267</v>
+        <v>147</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>147</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>290</v>
+        <v>147</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>147</v>
@@ -2768,28 +2858,28 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>283</v>
+        <v>260</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>109</v>
+        <v>124</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>56</v>
@@ -2801,10 +2891,10 @@
         <v>147</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>289</v>
+        <v>147</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>147</v>
@@ -2812,19 +2902,19 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>326</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>53</v>
@@ -2833,22 +2923,22 @@
         <v>15</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>56</v>
+        <v>151</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>265</v>
+        <v>147</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>147</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>290</v>
+        <v>147</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>291</v>
+        <v>147</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>147</v>
@@ -2856,43 +2946,43 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>320</v>
+        <v>54</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>329</v>
+        <v>281</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>147</v>
+        <v>303</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>128</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>322</v>
+        <v>55</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>56</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>147</v>
+        <v>267</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>147</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>147</v>
+        <v>290</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>147</v>
+        <v>310</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>147</v>
@@ -2900,19 +2990,19 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>316</v>
+        <v>25</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>317</v>
+        <v>26</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>257</v>
+        <v>283</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>147</v>
+        <v>108</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>52</v>
@@ -2921,7 +3011,7 @@
         <v>15</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>56</v>
@@ -2933,86 +3023,86 @@
         <v>147</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>147</v>
+        <v>289</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="32" spans="1:14" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="7" t="s">
-        <v>189</v>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="F32" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F32" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G32" s="7" t="s">
+      <c r="G32" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H32" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="K32" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="L32" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="M32" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="N32" s="7" t="s">
-        <v>77</v>
+      <c r="H32" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="N32" s="2" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>194</v>
+        <v>318</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>196</v>
+        <v>319</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>284</v>
+        <v>328</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>197</v>
+        <v>320</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>147</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>195</v>
+        <v>321</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>147</v>
@@ -3026,37 +3116,37 @@
       <c r="M33" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="N33" s="7" t="s">
-        <v>77</v>
+      <c r="N33" s="2" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>198</v>
+        <v>315</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>199</v>
+        <v>316</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>285</v>
+        <v>257</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>201</v>
+        <v>317</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="I34" s="7" t="s">
-        <v>137</v>
+        <v>48</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>147</v>
@@ -3070,48 +3160,48 @@
       <c r="M34" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="N34" s="7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>203</v>
+      <c r="N34" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="7" t="s">
+        <v>189</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>205</v>
+        <v>193</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>190</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="F35" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F35" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="G35" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H35" s="2" t="s">
-        <v>195</v>
+      <c r="H35" s="7" t="s">
+        <v>192</v>
       </c>
       <c r="I35" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="J35" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="M35" s="2" t="s">
+      <c r="J35" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="L35" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="M35" s="7" t="s">
         <v>147</v>
       </c>
       <c r="N35" s="7" t="s">
@@ -3120,19 +3210,19 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>209</v>
+        <v>197</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>53</v>
@@ -3143,7 +3233,7 @@
       <c r="H36" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="I36" s="7" t="s">
+      <c r="I36" s="2" t="s">
         <v>137</v>
       </c>
       <c r="J36" s="2" t="s">
@@ -3164,19 +3254,19 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>214</v>
+        <v>198</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>199</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>262</v>
+        <v>285</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>53</v>
@@ -3185,7 +3275,7 @@
         <v>15</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="I37" s="7" t="s">
         <v>137</v>
@@ -3208,19 +3298,19 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>53</v>
@@ -3252,19 +3342,19 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>53</v>
@@ -3296,19 +3386,19 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>225</v>
+        <v>211</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>214</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>53</v>
@@ -3340,19 +3430,19 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>53</v>
@@ -3384,19 +3474,19 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>53</v>
@@ -3428,19 +3518,19 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>53</v>
@@ -3472,19 +3562,19 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>53</v>
@@ -3516,19 +3606,19 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>262</v>
+        <v>286</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>53</v>
@@ -3560,19 +3650,19 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>161</v>
+        <v>235</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>162</v>
+        <v>236</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>324</v>
+        <v>286</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>163</v>
+        <v>237</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>164</v>
+        <v>238</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>53</v>
@@ -3581,42 +3671,42 @@
         <v>15</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>56</v>
+        <v>195</v>
+      </c>
+      <c r="I46" s="7" t="s">
+        <v>137</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>265</v>
+        <v>147</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>265</v>
+        <v>147</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="N46" s="2" t="s">
-        <v>254</v>
+        <v>147</v>
+      </c>
+      <c r="N46" s="7" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>65</v>
+        <v>239</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>66</v>
+        <v>240</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>104</v>
+        <v>286</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>242</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>53</v>
@@ -3625,42 +3715,42 @@
         <v>15</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>56</v>
+        <v>195</v>
+      </c>
+      <c r="I47" s="7" t="s">
+        <v>137</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>265</v>
+        <v>147</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>265</v>
+        <v>147</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="N47" s="2" t="s">
-        <v>254</v>
+        <v>147</v>
+      </c>
+      <c r="N47" s="7" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>67</v>
+        <v>243</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>24</v>
+        <v>244</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>324</v>
+        <v>262</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>307</v>
+        <v>245</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>246</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>53</v>
@@ -3669,42 +3759,42 @@
         <v>15</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>152</v>
+        <v>195</v>
+      </c>
+      <c r="I48" s="7" t="s">
+        <v>137</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>265</v>
+        <v>147</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>265</v>
+        <v>147</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="N48" s="2" t="s">
-        <v>254</v>
+        <v>147</v>
+      </c>
+      <c r="N48" s="7" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>339</v>
+        <v>161</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>337</v>
+        <v>162</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>340</v>
+        <v>163</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>341</v>
+        <v>164</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>53</v>
@@ -3713,154 +3803,154 @@
         <v>15</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>342</v>
+        <v>55</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>152</v>
+        <v>56</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>147</v>
+        <v>265</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>147</v>
+        <v>265</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>147</v>
+        <v>275</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>147</v>
+        <v>254</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>354</v>
+        <v>66</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>356</v>
+        <v>323</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>355</v>
+        <v>46</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>151</v>
+        <v>56</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>147</v>
+        <v>265</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>147</v>
+        <v>265</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>290</v>
+        <v>131</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>147</v>
+        <v>275</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>147</v>
+        <v>254</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>359</v>
+        <v>67</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>360</v>
+        <v>24</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>282</v>
+        <v>323</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>362</v>
+        <v>306</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>307</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>363</v>
+        <v>47</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>56</v>
+        <v>152</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>147</v>
+        <v>265</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>147</v>
+        <v>265</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>147</v>
+        <v>275</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>147</v>
+        <v>254</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>30</v>
+        <v>338</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>336</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>125</v>
+        <v>339</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>113</v>
+        <v>340</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>49</v>
+        <v>341</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>56</v>
+        <v>152</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>265</v>
+        <v>147</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>264</v>
+        <v>147</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>292</v>
+        <v>147</v>
       </c>
       <c r="N52" s="2" t="s">
         <v>147</v>
@@ -3868,31 +3958,31 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>31</v>
+        <v>352</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>353</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>115</v>
+        <v>356</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>116</v>
+        <v>355</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>52</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>51</v>
+        <v>354</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>56</v>
+        <v>151</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>147</v>
@@ -3904,7 +3994,7 @@
         <v>290</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>293</v>
+        <v>147</v>
       </c>
       <c r="N53" s="2" t="s">
         <v>147</v>
@@ -3912,28 +4002,28 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>348</v>
+        <v>358</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>359</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="D54" t="s">
-        <v>350</v>
+        <v>282</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>360</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>52</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>51</v>
+        <v>362</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>56</v>
@@ -3945,7 +4035,7 @@
         <v>147</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="M54" s="2" t="s">
         <v>147</v>
@@ -3956,43 +4046,43 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>32</v>
+        <v>364</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>363</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>126</v>
+        <v>365</v>
+      </c>
+      <c r="D55" t="s">
+        <v>366</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>119</v>
+        <v>367</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>52</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>43</v>
+        <v>202</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>267</v>
+        <v>147</v>
       </c>
       <c r="K55" s="2" t="s">
         <v>147</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>290</v>
+        <v>131</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>308</v>
+        <v>147</v>
       </c>
       <c r="N55" s="2" t="s">
         <v>147</v>
@@ -4000,28 +4090,28 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>33</v>
+        <v>377</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>374</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>296</v>
+        <v>260</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>118</v>
+        <v>375</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>117</v>
+        <v>376</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>52</v>
+        <v>150</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>56</v>
@@ -4033,10 +4123,10 @@
         <v>147</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>290</v>
+        <v>154</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>294</v>
+        <v>147</v>
       </c>
       <c r="N56" s="2" t="s">
         <v>147</v>
@@ -4044,19 +4134,19 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>297</v>
+        <v>329</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>52</v>
@@ -4065,22 +4155,22 @@
         <v>29</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>56</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="M57" s="5" t="s">
-        <v>309</v>
+      <c r="M57" s="2" t="s">
+        <v>292</v>
       </c>
       <c r="N57" s="2" t="s">
         <v>147</v>
@@ -4088,19 +4178,19 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>298</v>
+        <v>326</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>52</v>
@@ -4109,7 +4199,7 @@
         <v>29</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>56</v>
@@ -4121,10 +4211,10 @@
         <v>147</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>131</v>
+        <v>290</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="N58" s="2" t="s">
         <v>147</v>
@@ -4132,19 +4222,19 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>39</v>
+        <v>351</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>347</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>136</v>
+        <v>348</v>
+      </c>
+      <c r="D59" t="s">
+        <v>349</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>135</v>
+        <v>350</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>52</v>
@@ -4153,22 +4243,22 @@
         <v>29</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>137</v>
+        <v>56</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>268</v>
+        <v>147</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>265</v>
+        <v>147</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>300</v>
+        <v>147</v>
       </c>
       <c r="N59" s="2" t="s">
         <v>147</v>
@@ -4176,19 +4266,19 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>312</v>
+        <v>130</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>313</v>
+        <v>126</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>314</v>
+        <v>119</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>52</v>
@@ -4197,22 +4287,22 @@
         <v>29</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>56</v>
+        <v>153</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>147</v>
+        <v>267</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>147</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>131</v>
+        <v>290</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="N60" s="2" t="s">
         <v>147</v>
@@ -4220,19 +4310,19 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>180</v>
+        <v>74</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>324</v>
+        <v>296</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>182</v>
+        <v>118</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>183</v>
+        <v>117</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>52</v>
@@ -4241,42 +4331,42 @@
         <v>29</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>184</v>
+        <v>43</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>152</v>
+        <v>56</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>265</v>
+        <v>147</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>265</v>
+        <v>147</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>131</v>
+        <v>290</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>254</v>
+        <v>147</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>72</v>
+        <v>75</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>80</v>
+        <v>297</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>52</v>
@@ -4288,10 +4378,10 @@
         <v>43</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>152</v>
+        <v>56</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="K62" s="2" t="s">
         <v>265</v>
@@ -4299,28 +4389,28 @@
       <c r="L62" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="M62" s="2" t="s">
-        <v>275</v>
+      <c r="M62" s="5" t="s">
+        <v>309</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>254</v>
+        <v>147</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>247</v>
+        <v>76</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>35</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>324</v>
+        <v>298</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>186</v>
+        <v>121</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>187</v>
+        <v>122</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>52</v>
@@ -4329,42 +4419,42 @@
         <v>29</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>188</v>
+        <v>43</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>152</v>
+        <v>56</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>265</v>
+        <v>147</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>265</v>
+        <v>147</v>
       </c>
       <c r="L63" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>275</v>
+        <v>295</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>254</v>
+        <v>147</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>343</v>
+        <v>38</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>347</v>
+        <v>39</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>344</v>
+        <v>299</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="E64" s="5" t="s">
-        <v>346</v>
+        <v>136</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>135</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>52</v>
@@ -4376,73 +4466,337 @@
         <v>43</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>56</v>
+        <v>137</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>147</v>
+        <v>268</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>147</v>
+        <v>265</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>147</v>
+        <v>300</v>
       </c>
       <c r="N64" s="2" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B65" s="5"/>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D70" s="4"/>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B74" s="3"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B75" s="5"/>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B76" s="5"/>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A77" s="3"/>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B78" s="3"/>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A79" s="3"/>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A80" s="3"/>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" s="3"/>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A82" s="3"/>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A85" s="5"/>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L65" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="M65" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="N65" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="M66" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="N66" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="M67" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="N67" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="M68" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="N68" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="L69" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="M69" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="N69" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L70" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="M70" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="N70" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B71" s="5"/>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D76" s="4"/>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B80" s="3"/>
+      <c r="D80" s="4"/>
+      <c r="E80" s="4"/>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B81" s="5"/>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B82" s="5"/>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" s="3"/>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B84" s="3"/>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" s="3"/>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="3"/>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="3"/>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" s="3"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A89" s="3"/>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A91" s="5"/>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A92" s="3"/>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A93" s="3"/>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A94" s="3"/>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A95" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
@@ -4450,117 +4804,118 @@
     <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="B3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="B5" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="B7" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="B11" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="B12" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="B15" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="B20" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="B21" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="B22" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="B23" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="B47" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="B24" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="B26" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="B62" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="B52" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="B53" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="B55" r:id="rId18" location="tabStart" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="B56" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="B57" r:id="rId20" location="tabOA" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="B58" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="B10" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="B9" r:id="rId23" xr:uid="{2E978BF9-FAC6-4434-8A61-095820344F8E}"/>
+    <hyperlink ref="B8" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="B12" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="B13" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="B16" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="B22" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="B24" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="B25" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="B26" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="B50" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="B27" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="B29" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="B67" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="B57" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="B58" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="B60" r:id="rId18" location="tabStart" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="B61" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="B62" r:id="rId20" location="tabOA" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="B63" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="B11" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="B10" r:id="rId23" xr:uid="{2E978BF9-FAC6-4434-8A61-095820344F8E}"/>
     <hyperlink ref="B6" r:id="rId24" xr:uid="{7DE1F29E-C0EB-4D5D-AE2E-454D5BEF365B}"/>
-    <hyperlink ref="B29" r:id="rId25" xr:uid="{3B9FAA60-C30C-46CE-96E3-EE5C81E2F539}"/>
-    <hyperlink ref="B25" r:id="rId26" xr:uid="{4D50D363-EC52-4C94-B2F7-1696191B5D4E}"/>
-    <hyperlink ref="B48" r:id="rId27" xr:uid="{B9C038C6-1B26-46B2-9989-388377D3A1E4}"/>
-    <hyperlink ref="B28" r:id="rId28" xr:uid="{F77EA1F6-9ABC-4FEF-B834-6397EA503F9C}"/>
-    <hyperlink ref="B27" r:id="rId29" xr:uid="{E7B74F71-7B2B-4907-B7F2-A8ADE38CD488}"/>
+    <hyperlink ref="B32" r:id="rId25" xr:uid="{3B9FAA60-C30C-46CE-96E3-EE5C81E2F539}"/>
+    <hyperlink ref="B28" r:id="rId26" xr:uid="{4D50D363-EC52-4C94-B2F7-1696191B5D4E}"/>
+    <hyperlink ref="B51" r:id="rId27" xr:uid="{B9C038C6-1B26-46B2-9989-388377D3A1E4}"/>
+    <hyperlink ref="B31" r:id="rId28" xr:uid="{F77EA1F6-9ABC-4FEF-B834-6397EA503F9C}"/>
+    <hyperlink ref="B30" r:id="rId29" xr:uid="{E7B74F71-7B2B-4907-B7F2-A8ADE38CD488}"/>
     <hyperlink ref="E3" r:id="rId30" xr:uid="{3ADB5C4A-E316-42AC-AEB5-5C03EBAA513E}"/>
-    <hyperlink ref="E62" r:id="rId31" xr:uid="{9601B733-7355-4C0B-9C0E-F6BCC4EA8DE9}"/>
-    <hyperlink ref="E12" r:id="rId32" xr:uid="{D541F439-354D-4A23-AC17-3748FA08F9A2}"/>
-    <hyperlink ref="E52" r:id="rId33" xr:uid="{6232C42B-B80A-40CE-858B-59ED7C0E2E04}"/>
-    <hyperlink ref="E53" r:id="rId34" xr:uid="{58801C6C-6A1C-4AEC-BC83-814992A0795E}"/>
-    <hyperlink ref="E55" r:id="rId35" display="https://ror.org/001w7jn25" xr:uid="{F9BD791C-817E-4AD2-9AC8-EE07210D4210}"/>
-    <hyperlink ref="E56" r:id="rId36" xr:uid="{A8AE3B95-8296-4F85-B144-496311EE9374}"/>
-    <hyperlink ref="E57" r:id="rId37" display="https://ror.org/046ak2485" xr:uid="{C29AA756-D996-4217-891B-97B7A3C30910}"/>
-    <hyperlink ref="E58" r:id="rId38" xr:uid="{1D2EE263-E95F-46C3-AF25-593CA4061797}"/>
+    <hyperlink ref="E67" r:id="rId31" xr:uid="{9601B733-7355-4C0B-9C0E-F6BCC4EA8DE9}"/>
+    <hyperlink ref="E13" r:id="rId32" xr:uid="{D541F439-354D-4A23-AC17-3748FA08F9A2}"/>
+    <hyperlink ref="E57" r:id="rId33" xr:uid="{6232C42B-B80A-40CE-858B-59ED7C0E2E04}"/>
+    <hyperlink ref="E58" r:id="rId34" xr:uid="{58801C6C-6A1C-4AEC-BC83-814992A0795E}"/>
+    <hyperlink ref="E60" r:id="rId35" display="https://ror.org/001w7jn25" xr:uid="{F9BD791C-817E-4AD2-9AC8-EE07210D4210}"/>
+    <hyperlink ref="E61" r:id="rId36" xr:uid="{A8AE3B95-8296-4F85-B144-496311EE9374}"/>
+    <hyperlink ref="E62" r:id="rId37" display="https://ror.org/046ak2485" xr:uid="{C29AA756-D996-4217-891B-97B7A3C30910}"/>
+    <hyperlink ref="E63" r:id="rId38" xr:uid="{1D2EE263-E95F-46C3-AF25-593CA4061797}"/>
     <hyperlink ref="E2" r:id="rId39" xr:uid="{7CDDC8F0-EDA1-45AE-808E-11EDE8ED16C8}"/>
     <hyperlink ref="E5" r:id="rId40" xr:uid="{3A0FC5E2-BB0B-491F-A2BB-C21F3A80CBE7}"/>
     <hyperlink ref="E6" r:id="rId41" xr:uid="{2BC3348D-A624-44A6-8799-21F5E041567A}"/>
-    <hyperlink ref="E7" r:id="rId42" xr:uid="{49E8E0D9-383D-42D7-9AF6-3E2FD4C3D862}"/>
-    <hyperlink ref="E15" r:id="rId43" xr:uid="{00F61FBB-F72F-4352-9284-450ECA9D60FD}"/>
-    <hyperlink ref="E20" r:id="rId44" xr:uid="{03D2F215-D7E2-4E90-95E5-D96F3C7FE7B0}"/>
-    <hyperlink ref="E21" r:id="rId45" xr:uid="{13E8F539-3D8B-4DB6-9E71-42470F81BB7E}"/>
-    <hyperlink ref="E22" r:id="rId46" xr:uid="{6F1A044C-43C2-41DC-AE79-F807D75A0BE4}"/>
-    <hyperlink ref="E24" r:id="rId47" xr:uid="{0548E347-4912-43D7-A622-2508B2333351}"/>
-    <hyperlink ref="E27" r:id="rId48" xr:uid="{A8AAA73B-8AA0-4286-8546-B00725169F40}"/>
-    <hyperlink ref="E8" r:id="rId49" xr:uid="{AA26F3F5-37F5-4224-8CD6-D258C4FAA10D}"/>
-    <hyperlink ref="E59" r:id="rId50" xr:uid="{33BA3911-157F-4B5F-B224-926A665413ED}"/>
-    <hyperlink ref="B8" r:id="rId51" xr:uid="{09FCB9D2-25B2-4442-A69D-77E3413519EF}"/>
-    <hyperlink ref="B59" r:id="rId52" xr:uid="{4B739AEA-7F3F-45D6-B075-72568EA43671}"/>
-    <hyperlink ref="E46" r:id="rId53" xr:uid="{11697F8A-9521-43AE-95AC-F7C8DC927828}"/>
-    <hyperlink ref="E16" r:id="rId54" xr:uid="{00FFFA05-4F61-43C4-B140-6BB688AA3AB5}"/>
-    <hyperlink ref="E18" r:id="rId55" xr:uid="{BCDD8F9A-1A73-459B-BD95-87BA9F6737EA}"/>
-    <hyperlink ref="E61" r:id="rId56" xr:uid="{983DC9EF-701A-429D-80E1-7BCF0B0AB211}"/>
-    <hyperlink ref="E63" r:id="rId57" xr:uid="{CA6D0EA0-A9E8-4135-8FF7-6D68CDEAA7CD}"/>
-    <hyperlink ref="E32" r:id="rId58" xr:uid="{0CDA4E31-1E14-4458-A0AC-AD565254D257}"/>
-    <hyperlink ref="E34" r:id="rId59" xr:uid="{DF544658-C5B8-453E-A253-D7E24EC78999}"/>
-    <hyperlink ref="B32" r:id="rId60" location="/summary" xr:uid="{6617F167-467C-4718-B0F8-7422A40D657C}"/>
-    <hyperlink ref="B33" r:id="rId61" location="/summary" xr:uid="{D707AE61-570C-49AE-B9DC-D195F480CC89}"/>
-    <hyperlink ref="B34" r:id="rId62" location="/summary" xr:uid="{7050ECBE-B39D-4188-A1DB-1F6498B19379}"/>
-    <hyperlink ref="B35" r:id="rId63" location="/summary" xr:uid="{F4063A92-6CF9-4519-A8CE-5245FE566D22}"/>
-    <hyperlink ref="E35" r:id="rId64" xr:uid="{BEC528C8-8C37-4AFF-8D8B-8F8D3A240634}"/>
-    <hyperlink ref="E36" r:id="rId65" xr:uid="{7D224445-7408-46E9-88C2-52F1B75BFEAF}"/>
-    <hyperlink ref="E37" r:id="rId66" xr:uid="{39334884-B6DA-4302-B757-40B7BEFC4991}"/>
-    <hyperlink ref="E38" r:id="rId67" xr:uid="{0A2A441D-066B-4178-AD23-8AA09BB30D75}"/>
-    <hyperlink ref="E39" r:id="rId68" xr:uid="{3F6F95ED-3318-4EFC-A987-FEB499202E55}"/>
-    <hyperlink ref="E40" r:id="rId69" xr:uid="{AEA0BFE3-2655-4641-9BA5-B7AEE964290C}"/>
-    <hyperlink ref="E41" r:id="rId70" xr:uid="{471D72C3-718C-4EA8-9884-4F9A9E8380DA}"/>
-    <hyperlink ref="E42" r:id="rId71" xr:uid="{0D432010-5CC9-48E7-975A-868C0D49E444}"/>
-    <hyperlink ref="E43" r:id="rId72" xr:uid="{D7378B5E-D770-4815-B178-8642F285B003}"/>
-    <hyperlink ref="E44" r:id="rId73" xr:uid="{78F89174-3E82-4469-9590-D517139B1874}"/>
-    <hyperlink ref="E45" r:id="rId74" xr:uid="{1BE7C807-93C8-4BA5-8555-C2915E893FD7}"/>
-    <hyperlink ref="B13" r:id="rId75" xr:uid="{7EC06670-BCC6-4C28-8990-16D6ED8D1B75}"/>
-    <hyperlink ref="B46" r:id="rId76" xr:uid="{FAE396B9-6111-43D9-AD97-A83A04299C85}"/>
-    <hyperlink ref="B14" r:id="rId77" xr:uid="{15216A1B-A2C9-49F0-AC6D-689D9B21244A}"/>
-    <hyperlink ref="B16" r:id="rId78" xr:uid="{CF4AF49A-0AC7-4B2E-B50E-A7C581697FD0}"/>
-    <hyperlink ref="B17" r:id="rId79" xr:uid="{E6653F73-E021-4393-A2D2-29A5B1C99900}"/>
-    <hyperlink ref="B18" r:id="rId80" xr:uid="{F6AC3892-79FB-4721-BB15-FEA70165FAA2}"/>
-    <hyperlink ref="B61" r:id="rId81" xr:uid="{7BE9EA28-27E4-467C-8A7D-B08206A8C247}"/>
-    <hyperlink ref="B63" r:id="rId82" xr:uid="{FCFA5DBC-E4A3-42D2-B584-E1B3C050FA12}"/>
-    <hyperlink ref="B36" r:id="rId83" location="/summary" xr:uid="{BD5570CD-2974-47D3-BECD-FBF1A0103586}"/>
-    <hyperlink ref="B38" r:id="rId84" location="/summary" xr:uid="{A04BAB6F-1883-444C-A660-93173657731B}"/>
-    <hyperlink ref="B39" r:id="rId85" location="/summary" xr:uid="{AFDD9191-F1EA-4D82-B791-F8D71B79299A}"/>
-    <hyperlink ref="B40" r:id="rId86" location="/summary" xr:uid="{57774DD1-A02B-4AE1-9973-904AB3BE5B36}"/>
-    <hyperlink ref="B41" r:id="rId87" location="/summary" xr:uid="{A903A446-66CD-4C34-AC30-CCCF3C6C296C}"/>
-    <hyperlink ref="B42" r:id="rId88" location="/summary" xr:uid="{36DB8854-B664-4B45-86B1-71A127F221B0}"/>
-    <hyperlink ref="B43" r:id="rId89" location="/summary" xr:uid="{16694492-06E8-45D8-8D1B-B8A3DF4AC9D5}"/>
-    <hyperlink ref="B44" r:id="rId90" location="/summary" xr:uid="{9854F6E8-3E5F-4518-8944-1A4E66D48382}"/>
-    <hyperlink ref="B45" r:id="rId91" location="/summary" xr:uid="{883A199B-7D7C-4FFD-940B-86C5AC4651EF}"/>
-    <hyperlink ref="E23" r:id="rId92" xr:uid="{5D61A60F-EF84-46C4-818E-92709384E491}"/>
-    <hyperlink ref="E26" r:id="rId93" xr:uid="{B8F94E19-DD69-45F7-8CDC-C62BF5BB5A59}"/>
-    <hyperlink ref="E28" r:id="rId94" xr:uid="{749551B2-B6C1-4DC8-977F-D0A40E9FB7CB}"/>
-    <hyperlink ref="E29" r:id="rId95" xr:uid="{DB97BB73-2C5C-4BB7-AAD1-9F3E73AEF9FA}"/>
-    <hyperlink ref="E47" r:id="rId96" xr:uid="{7F0954D5-9E77-46DF-8A79-7B7D5CDD9561}"/>
+    <hyperlink ref="E8" r:id="rId42" xr:uid="{49E8E0D9-383D-42D7-9AF6-3E2FD4C3D862}"/>
+    <hyperlink ref="E16" r:id="rId43" xr:uid="{00F61FBB-F72F-4352-9284-450ECA9D60FD}"/>
+    <hyperlink ref="E22" r:id="rId44" xr:uid="{03D2F215-D7E2-4E90-95E5-D96F3C7FE7B0}"/>
+    <hyperlink ref="E24" r:id="rId45" xr:uid="{13E8F539-3D8B-4DB6-9E71-42470F81BB7E}"/>
+    <hyperlink ref="E25" r:id="rId46" xr:uid="{6F1A044C-43C2-41DC-AE79-F807D75A0BE4}"/>
+    <hyperlink ref="E27" r:id="rId47" xr:uid="{0548E347-4912-43D7-A622-2508B2333351}"/>
+    <hyperlink ref="E30" r:id="rId48" xr:uid="{A8AAA73B-8AA0-4286-8546-B00725169F40}"/>
+    <hyperlink ref="E9" r:id="rId49" xr:uid="{AA26F3F5-37F5-4224-8CD6-D258C4FAA10D}"/>
+    <hyperlink ref="E64" r:id="rId50" xr:uid="{33BA3911-157F-4B5F-B224-926A665413ED}"/>
+    <hyperlink ref="B9" r:id="rId51" xr:uid="{09FCB9D2-25B2-4442-A69D-77E3413519EF}"/>
+    <hyperlink ref="B64" r:id="rId52" xr:uid="{4B739AEA-7F3F-45D6-B075-72568EA43671}"/>
+    <hyperlink ref="E49" r:id="rId53" xr:uid="{11697F8A-9521-43AE-95AC-F7C8DC927828}"/>
+    <hyperlink ref="E17" r:id="rId54" xr:uid="{00FFFA05-4F61-43C4-B140-6BB688AA3AB5}"/>
+    <hyperlink ref="E19" r:id="rId55" xr:uid="{BCDD8F9A-1A73-459B-BD95-87BA9F6737EA}"/>
+    <hyperlink ref="E66" r:id="rId56" xr:uid="{983DC9EF-701A-429D-80E1-7BCF0B0AB211}"/>
+    <hyperlink ref="E68" r:id="rId57" xr:uid="{CA6D0EA0-A9E8-4135-8FF7-6D68CDEAA7CD}"/>
+    <hyperlink ref="E35" r:id="rId58" xr:uid="{0CDA4E31-1E14-4458-A0AC-AD565254D257}"/>
+    <hyperlink ref="E37" r:id="rId59" xr:uid="{DF544658-C5B8-453E-A253-D7E24EC78999}"/>
+    <hyperlink ref="B35" r:id="rId60" location="/summary" xr:uid="{6617F167-467C-4718-B0F8-7422A40D657C}"/>
+    <hyperlink ref="B36" r:id="rId61" location="/summary" xr:uid="{D707AE61-570C-49AE-B9DC-D195F480CC89}"/>
+    <hyperlink ref="B37" r:id="rId62" location="/summary" xr:uid="{7050ECBE-B39D-4188-A1DB-1F6498B19379}"/>
+    <hyperlink ref="B38" r:id="rId63" location="/summary" xr:uid="{F4063A92-6CF9-4519-A8CE-5245FE566D22}"/>
+    <hyperlink ref="E38" r:id="rId64" xr:uid="{BEC528C8-8C37-4AFF-8D8B-8F8D3A240634}"/>
+    <hyperlink ref="E39" r:id="rId65" xr:uid="{7D224445-7408-46E9-88C2-52F1B75BFEAF}"/>
+    <hyperlink ref="E40" r:id="rId66" xr:uid="{39334884-B6DA-4302-B757-40B7BEFC4991}"/>
+    <hyperlink ref="E41" r:id="rId67" xr:uid="{0A2A441D-066B-4178-AD23-8AA09BB30D75}"/>
+    <hyperlink ref="E42" r:id="rId68" xr:uid="{3F6F95ED-3318-4EFC-A987-FEB499202E55}"/>
+    <hyperlink ref="E43" r:id="rId69" xr:uid="{AEA0BFE3-2655-4641-9BA5-B7AEE964290C}"/>
+    <hyperlink ref="E44" r:id="rId70" xr:uid="{471D72C3-718C-4EA8-9884-4F9A9E8380DA}"/>
+    <hyperlink ref="E45" r:id="rId71" xr:uid="{0D432010-5CC9-48E7-975A-868C0D49E444}"/>
+    <hyperlink ref="E46" r:id="rId72" xr:uid="{D7378B5E-D770-4815-B178-8642F285B003}"/>
+    <hyperlink ref="E47" r:id="rId73" xr:uid="{78F89174-3E82-4469-9590-D517139B1874}"/>
+    <hyperlink ref="E48" r:id="rId74" xr:uid="{1BE7C807-93C8-4BA5-8555-C2915E893FD7}"/>
+    <hyperlink ref="B14" r:id="rId75" xr:uid="{7EC06670-BCC6-4C28-8990-16D6ED8D1B75}"/>
+    <hyperlink ref="B49" r:id="rId76" xr:uid="{FAE396B9-6111-43D9-AD97-A83A04299C85}"/>
+    <hyperlink ref="B15" r:id="rId77" xr:uid="{15216A1B-A2C9-49F0-AC6D-689D9B21244A}"/>
+    <hyperlink ref="B17" r:id="rId78" xr:uid="{CF4AF49A-0AC7-4B2E-B50E-A7C581697FD0}"/>
+    <hyperlink ref="B18" r:id="rId79" xr:uid="{E6653F73-E021-4393-A2D2-29A5B1C99900}"/>
+    <hyperlink ref="B19" r:id="rId80" xr:uid="{F6AC3892-79FB-4721-BB15-FEA70165FAA2}"/>
+    <hyperlink ref="B66" r:id="rId81" xr:uid="{7BE9EA28-27E4-467C-8A7D-B08206A8C247}"/>
+    <hyperlink ref="B68" r:id="rId82" xr:uid="{FCFA5DBC-E4A3-42D2-B584-E1B3C050FA12}"/>
+    <hyperlink ref="B39" r:id="rId83" location="/summary" xr:uid="{BD5570CD-2974-47D3-BECD-FBF1A0103586}"/>
+    <hyperlink ref="B41" r:id="rId84" location="/summary" xr:uid="{A04BAB6F-1883-444C-A660-93173657731B}"/>
+    <hyperlink ref="B42" r:id="rId85" location="/summary" xr:uid="{AFDD9191-F1EA-4D82-B791-F8D71B79299A}"/>
+    <hyperlink ref="B43" r:id="rId86" location="/summary" xr:uid="{57774DD1-A02B-4AE1-9973-904AB3BE5B36}"/>
+    <hyperlink ref="B44" r:id="rId87" location="/summary" xr:uid="{A903A446-66CD-4C34-AC30-CCCF3C6C296C}"/>
+    <hyperlink ref="B45" r:id="rId88" location="/summary" xr:uid="{36DB8854-B664-4B45-86B1-71A127F221B0}"/>
+    <hyperlink ref="B46" r:id="rId89" location="/summary" xr:uid="{16694492-06E8-45D8-8D1B-B8A3DF4AC9D5}"/>
+    <hyperlink ref="B47" r:id="rId90" location="/summary" xr:uid="{9854F6E8-3E5F-4518-8944-1A4E66D48382}"/>
+    <hyperlink ref="B48" r:id="rId91" location="/summary" xr:uid="{883A199B-7D7C-4FFD-940B-86C5AC4651EF}"/>
+    <hyperlink ref="E26" r:id="rId92" xr:uid="{5D61A60F-EF84-46C4-818E-92709384E491}"/>
+    <hyperlink ref="E29" r:id="rId93" xr:uid="{B8F94E19-DD69-45F7-8CDC-C62BF5BB5A59}"/>
+    <hyperlink ref="E31" r:id="rId94" xr:uid="{749551B2-B6C1-4DC8-977F-D0A40E9FB7CB}"/>
+    <hyperlink ref="E32" r:id="rId95" xr:uid="{DB97BB73-2C5C-4BB7-AAD1-9F3E73AEF9FA}"/>
+    <hyperlink ref="E50" r:id="rId96" xr:uid="{7F0954D5-9E77-46DF-8A79-7B7D5CDD9561}"/>
     <hyperlink ref="B4" r:id="rId97" xr:uid="{52B7C2FF-613F-441D-B747-455011D88B94}"/>
     <hyperlink ref="M4" r:id="rId98" xr:uid="{25F22962-E187-47E7-8740-E5480B5E0924}"/>
     <hyperlink ref="M5" r:id="rId99" display="https://open.coki.ac/data/" xr:uid="{DB2ED5D1-682A-4FEC-8903-1DDA7A54D005}"/>
     <hyperlink ref="M2" r:id="rId100" xr:uid="{BAC31D3C-8E3A-4527-A22B-4B4925B7E268}"/>
     <hyperlink ref="M3" r:id="rId101" xr:uid="{1590F783-A4BA-42E1-85A5-DD3C31BC85F1}"/>
-    <hyperlink ref="M57" r:id="rId102" display="https://doi.org/10.5281/zenodo.14627194" xr:uid="{7505D7BB-66C2-4946-842B-C435F7CBDBBA}"/>
-    <hyperlink ref="B60" r:id="rId103" xr:uid="{1C43044B-9080-4167-A7D9-997EC0FFC79E}"/>
-    <hyperlink ref="E60" r:id="rId104" xr:uid="{EA10523E-0AE4-4617-A677-8EFF38033C92}"/>
-    <hyperlink ref="B31" r:id="rId105" xr:uid="{686ADC90-E960-4F15-968A-1B3CF6560964}"/>
-    <hyperlink ref="B30" r:id="rId106" xr:uid="{8F493C13-3C3A-4E8A-B0B6-3282B660B08B}"/>
-    <hyperlink ref="E49" r:id="rId107" xr:uid="{862594BE-511B-4D5C-A6BF-57090C6388C3}"/>
-    <hyperlink ref="B64" r:id="rId108" xr:uid="{96FC04AF-877C-431F-B3F8-4D1E19D472E6}"/>
-    <hyperlink ref="E64" r:id="rId109" xr:uid="{45CD4A49-4D8B-4A86-9590-D2A3B3CCB9E1}"/>
-    <hyperlink ref="E51" r:id="rId110" xr:uid="{2FF66816-4CE0-4F46-A861-704CA4428860}"/>
-    <hyperlink ref="E50" r:id="rId111" xr:uid="{FDB3B9A7-AD57-41D9-B416-0C44DFE82446}"/>
+    <hyperlink ref="M62" r:id="rId102" display="https://doi.org/10.5281/zenodo.14627194" xr:uid="{7505D7BB-66C2-4946-842B-C435F7CBDBBA}"/>
+    <hyperlink ref="B65" r:id="rId103" xr:uid="{1C43044B-9080-4167-A7D9-997EC0FFC79E}"/>
+    <hyperlink ref="E65" r:id="rId104" xr:uid="{EA10523E-0AE4-4617-A677-8EFF38033C92}"/>
+    <hyperlink ref="B34" r:id="rId105" xr:uid="{686ADC90-E960-4F15-968A-1B3CF6560964}"/>
+    <hyperlink ref="B33" r:id="rId106" xr:uid="{8F493C13-3C3A-4E8A-B0B6-3282B660B08B}"/>
+    <hyperlink ref="E52" r:id="rId107" xr:uid="{862594BE-511B-4D5C-A6BF-57090C6388C3}"/>
+    <hyperlink ref="B70" r:id="rId108" xr:uid="{96FC04AF-877C-431F-B3F8-4D1E19D472E6}"/>
+    <hyperlink ref="E70" r:id="rId109" xr:uid="{45CD4A49-4D8B-4A86-9590-D2A3B3CCB9E1}"/>
+    <hyperlink ref="E54" r:id="rId110" xr:uid="{2FF66816-4CE0-4F46-A861-704CA4428860}"/>
+    <hyperlink ref="E53" r:id="rId111" xr:uid="{FDB3B9A7-AD57-41D9-B416-0C44DFE82446}"/>
+    <hyperlink ref="E21" r:id="rId112" xr:uid="{6C405A8B-0725-44B0-B6A0-BE56C83BA259}"/>
   </hyperlinks>
   <pageMargins left="0" right="0" top="0.39409448818897608" bottom="0.39409448818897608" header="0" footer="0"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId112"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId113"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;A</oddHeader>
     <oddFooter>&amp;CPage &amp;P</oddFooter>

--- a/files/Dashboards_Website.xlsx
+++ b/files/Dashboards_Website.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jschneid\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BB83F33-B2CB-45F6-B420-925B9159067F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C1127BF-5374-48B7-A1EA-CB30AD46398D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="398">
   <si>
     <t>NAME</t>
   </si>
@@ -1222,6 +1222,18 @@
   </si>
   <si>
     <t>https://support.datacite.org/docs/datacite-metadata-dashboard</t>
+  </si>
+  <si>
+    <t>Publikations- und Kostenmonitoring in Nordrhein-Westfalen (pkm_nrw)</t>
+  </si>
+  <si>
+    <t>https://pkm-nrw.ub.uni-bielefeld.de/</t>
+  </si>
+  <si>
+    <t>openaccess.nrw, Ministerium für Kultur und Wissenschaft NRW</t>
+  </si>
+  <si>
+    <t>https://ror.org/04n00c532</t>
   </si>
 </sst>
 </file>
@@ -1651,24 +1663,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N95"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.19921875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.33203125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="27.296875" style="2" customWidth="1"/>
     <col min="2" max="2" width="15" style="2" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="10.796875" style="2" customWidth="1"/>
     <col min="4" max="4" width="49.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="20.83203125" style="2" customWidth="1"/>
-    <col min="6" max="8" width="11.1640625" style="2"/>
-    <col min="9" max="9" width="27.58203125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="17.83203125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="13.58203125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="13.4140625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="37.58203125" style="2" customWidth="1"/>
-    <col min="14" max="14" width="17.33203125" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="11.1640625" style="2"/>
+    <col min="5" max="5" width="20.796875" style="2" customWidth="1"/>
+    <col min="6" max="8" width="11.19921875" style="2"/>
+    <col min="9" max="9" width="27.59765625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="17.796875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="13.59765625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="13.3984375" style="2" customWidth="1"/>
+    <col min="13" max="13" width="37.59765625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="17.296875" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="11.19921875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1712,7 +1724,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>139</v>
       </c>
@@ -1756,7 +1768,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>140</v>
       </c>
@@ -1800,7 +1812,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>248</v>
       </c>
@@ -1844,7 +1856,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -1888,7 +1900,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>57</v>
       </c>
@@ -1932,7 +1944,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>382</v>
       </c>
@@ -1976,7 +1988,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -2020,7 +2032,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>253</v>
       </c>
@@ -2064,7 +2076,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
@@ -2108,7 +2120,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>36</v>
       </c>
@@ -2152,7 +2164,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
@@ -2196,7 +2208,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>61</v>
       </c>
@@ -2240,7 +2252,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>158</v>
       </c>
@@ -2284,7 +2296,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>165</v>
       </c>
@@ -2328,7 +2340,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>62</v>
       </c>
@@ -2372,7 +2384,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>169</v>
       </c>
@@ -2416,7 +2428,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>170</v>
       </c>
@@ -2460,7 +2472,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>176</v>
       </c>
@@ -2504,7 +2516,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>330</v>
       </c>
@@ -2548,7 +2560,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>392</v>
       </c>
@@ -2592,7 +2604,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>13</v>
       </c>
@@ -2636,7 +2648,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>370</v>
       </c>
@@ -2680,7 +2692,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>70</v>
       </c>
@@ -2724,7 +2736,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>18</v>
       </c>
@@ -2768,7 +2780,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>20</v>
       </c>
@@ -2812,7 +2824,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>22</v>
       </c>
@@ -2856,7 +2868,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>16</v>
       </c>
@@ -2900,7 +2912,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>69</v>
       </c>
@@ -2944,7 +2956,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>327</v>
       </c>
@@ -2988,7 +3000,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>25</v>
       </c>
@@ -3032,7 +3044,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>27</v>
       </c>
@@ -3076,7 +3088,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>318</v>
       </c>
@@ -3120,7 +3132,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>315</v>
       </c>
@@ -3164,7 +3176,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="35" spans="1:14" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
         <v>189</v>
       </c>
@@ -3208,7 +3220,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>194</v>
       </c>
@@ -3252,7 +3264,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>198</v>
       </c>
@@ -3296,7 +3308,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>203</v>
       </c>
@@ -3340,7 +3352,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>207</v>
       </c>
@@ -3384,7 +3396,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>211</v>
       </c>
@@ -3428,7 +3440,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>215</v>
       </c>
@@ -3472,7 +3484,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>219</v>
       </c>
@@ -3516,7 +3528,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>222</v>
       </c>
@@ -3560,7 +3572,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>227</v>
       </c>
@@ -3604,7 +3616,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>231</v>
       </c>
@@ -3648,7 +3660,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>235</v>
       </c>
@@ -3692,7 +3704,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>239</v>
       </c>
@@ -3736,7 +3748,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>243</v>
       </c>
@@ -3780,7 +3792,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>161</v>
       </c>
@@ -3824,7 +3836,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>65</v>
       </c>
@@ -3868,7 +3880,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>67</v>
       </c>
@@ -3912,7 +3924,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>338</v>
       </c>
@@ -3956,7 +3968,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>352</v>
       </c>
@@ -4000,7 +4012,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>358</v>
       </c>
@@ -4044,7 +4056,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>364</v>
       </c>
@@ -4088,7 +4100,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>377</v>
       </c>
@@ -4132,7 +4144,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>16</v>
       </c>
@@ -4176,7 +4188,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>73</v>
       </c>
@@ -4220,7 +4232,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>351</v>
       </c>
@@ -4264,7 +4276,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>130</v>
       </c>
@@ -4308,7 +4320,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>74</v>
       </c>
@@ -4352,7 +4364,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>75</v>
       </c>
@@ -4396,7 +4408,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>76</v>
       </c>
@@ -4440,7 +4452,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>38</v>
       </c>
@@ -4484,7 +4496,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>311</v>
       </c>
@@ -4528,7 +4540,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>181</v>
       </c>
@@ -4572,7 +4584,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>71</v>
       </c>
@@ -4616,7 +4628,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>185</v>
       </c>
@@ -4660,7 +4672,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>378</v>
       </c>
@@ -4704,7 +4716,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>342</v>
       </c>
@@ -4748,54 +4760,95 @@
         <v>147</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B71" s="5"/>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L71" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="M71" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="N71" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="D76" s="4"/>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B80" s="3"/>
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B81" s="5"/>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B82" s="5"/>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="3"/>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B84" s="3"/>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="3"/>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="3"/>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="3"/>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="3"/>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="5"/>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="3"/>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="3"/>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="3"/>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="3"/>
     </row>
   </sheetData>
@@ -4913,9 +4966,10 @@
     <hyperlink ref="E54" r:id="rId110" xr:uid="{2FF66816-4CE0-4F46-A861-704CA4428860}"/>
     <hyperlink ref="E53" r:id="rId111" xr:uid="{FDB3B9A7-AD57-41D9-B416-0C44DFE82446}"/>
     <hyperlink ref="E21" r:id="rId112" xr:uid="{6C405A8B-0725-44B0-B6A0-BE56C83BA259}"/>
+    <hyperlink ref="E71" r:id="rId113" xr:uid="{C9D2177C-462A-417A-BB7B-C092AD2A7539}"/>
   </hyperlinks>
   <pageMargins left="0" right="0" top="0.39409448818897608" bottom="0.39409448818897608" header="0" footer="0"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId113"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId114"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;A</oddHeader>
     <oddFooter>&amp;CPage &amp;P</oddFooter>
@@ -4926,10 +4980,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" customWidth="1"/>
-    <col min="2" max="2" width="11.1640625" customWidth="1"/>
+    <col min="1" max="1" width="10.69921875" customWidth="1"/>
+    <col min="2" max="2" width="11.19921875" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0" right="0" top="0.39409448818897608" bottom="0.39409448818897608" header="0" footer="0"/>
@@ -4943,10 +4997,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" customWidth="1"/>
-    <col min="2" max="2" width="11.1640625" customWidth="1"/>
+    <col min="1" max="1" width="10.69921875" customWidth="1"/>
+    <col min="2" max="2" width="11.19921875" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0" right="0" top="0.39409448818897608" bottom="0.39409448818897608" header="0" footer="0"/>

--- a/files/Dashboards_Website.xlsx
+++ b/files/Dashboards_Website.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jschneid\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C1127BF-5374-48B7-A1EA-CB30AD46398D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F7DFF1-FFE5-49EB-9D2F-01213F9CBAA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -806,9 +806,6 @@
     <t>2013–2023</t>
   </si>
   <si>
-    <t>2006–2022</t>
-  </si>
-  <si>
     <t>2017–2024</t>
   </si>
   <si>
@@ -1234,6 +1231,9 @@
   </si>
   <si>
     <t>https://ror.org/04n00c532</t>
+  </si>
+  <si>
+    <t>2006–2023</t>
   </si>
 </sst>
 </file>
@@ -1721,7 +1721,7 @@
         <v>251</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -1753,13 +1753,13 @@
         <v>56</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="M2" s="5" t="s">
         <v>252</v>
@@ -1776,7 +1776,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>256</v>
+        <v>397</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>86</v>
@@ -1800,13 +1800,13 @@
         <v>147</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>154</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>147</v>
@@ -1820,7 +1820,7 @@
         <v>249</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>256</v>
+        <v>397</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>86</v>
@@ -1841,10 +1841,10 @@
         <v>56</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>131</v>
@@ -1864,7 +1864,7 @@
         <v>5</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>123</v>
@@ -1885,16 +1885,16 @@
         <v>56</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>147</v>
@@ -1908,7 +1908,7 @@
         <v>60</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>90</v>
@@ -1929,16 +1929,16 @@
         <v>56</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>147</v>
@@ -1946,19 +1946,19 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="C7" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>385</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>386</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>150</v>
@@ -1976,13 +1976,13 @@
         <v>147</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>147</v>
@@ -1996,7 +1996,7 @@
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>91</v>
@@ -2017,16 +2017,16 @@
         <v>151</v>
       </c>
       <c r="J8" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>264</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>265</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N8" s="4" t="s">
         <v>147</v>
@@ -2040,7 +2040,7 @@
         <v>134</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>133</v>
@@ -2061,16 +2061,16 @@
         <v>56</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>147</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>147</v>
@@ -2084,7 +2084,7 @@
         <v>63</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>155</v>
@@ -2128,7 +2128,7 @@
         <v>37</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>78</v>
@@ -2149,7 +2149,7 @@
         <v>56</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>147</v>
@@ -2158,7 +2158,7 @@
         <v>147</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>147</v>
@@ -2172,7 +2172,7 @@
         <v>58</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>79</v>
@@ -2196,13 +2196,13 @@
         <v>147</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>147</v>
@@ -2216,7 +2216,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>93</v>
@@ -2237,16 +2237,16 @@
         <v>129</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>147</v>
@@ -2260,7 +2260,7 @@
         <v>159</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>160</v>
@@ -2281,16 +2281,16 @@
         <v>153</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>254</v>
@@ -2304,7 +2304,7 @@
         <v>166</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>167</v>
@@ -2325,16 +2325,16 @@
         <v>153</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>254</v>
@@ -2348,7 +2348,7 @@
         <v>64</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>12</v>
@@ -2369,16 +2369,16 @@
         <v>152</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>254</v>
@@ -2392,7 +2392,7 @@
         <v>168</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>174</v>
@@ -2413,16 +2413,16 @@
         <v>153</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>254</v>
@@ -2436,7 +2436,7 @@
         <v>171</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>173</v>
@@ -2457,16 +2457,16 @@
         <v>172</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N18" s="2" t="s">
         <v>254</v>
@@ -2480,7 +2480,7 @@
         <v>177</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>178</v>
@@ -2501,16 +2501,16 @@
         <v>137</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>254</v>
@@ -2518,16 +2518,16 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="C20" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>332</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>333</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>147</v>
@@ -2542,7 +2542,7 @@
         <v>10</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>147</v>
@@ -2554,7 +2554,7 @@
         <v>131</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>147</v>
@@ -2562,19 +2562,19 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B21" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="E21" s="5" t="s">
         <v>390</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>391</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>150</v>
@@ -2592,13 +2592,13 @@
         <v>147</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>147</v>
@@ -2612,7 +2612,7 @@
         <v>14</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>95</v>
@@ -2633,16 +2633,16 @@
         <v>152</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="N22" s="2" t="s">
         <v>147</v>
@@ -2650,19 +2650,19 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="5" t="s">
         <v>372</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>373</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>53</v>
@@ -2677,10 +2677,10 @@
         <v>137</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>131</v>
@@ -2700,7 +2700,7 @@
         <v>17</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>97</v>
@@ -2724,13 +2724,13 @@
         <v>147</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="N24" s="2" t="s">
         <v>147</v>
@@ -2744,7 +2744,7 @@
         <v>19</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>99</v>
@@ -2762,19 +2762,19 @@
         <v>44</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>147</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="N25" s="2" t="s">
         <v>147</v>
@@ -2788,7 +2788,7 @@
         <v>21</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>101</v>
@@ -2815,10 +2815,10 @@
         <v>147</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>147</v>
@@ -2832,7 +2832,7 @@
         <v>23</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>105</v>
@@ -2862,7 +2862,7 @@
         <v>147</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>147</v>
@@ -2876,7 +2876,7 @@
         <v>138</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>124</v>
@@ -2920,7 +2920,7 @@
         <v>68</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>82</v>
@@ -2958,16 +2958,16 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>54</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>128</v>
@@ -2985,16 +2985,16 @@
         <v>56</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>147</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>147</v>
@@ -3008,7 +3008,7 @@
         <v>26</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>108</v>
@@ -3038,7 +3038,7 @@
         <v>131</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>147</v>
@@ -3052,7 +3052,7 @@
         <v>28</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>110</v>
@@ -3073,16 +3073,16 @@
         <v>56</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>147</v>
       </c>
       <c r="L32" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="M32" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>291</v>
       </c>
       <c r="N32" s="2" t="s">
         <v>147</v>
@@ -3090,16 +3090,16 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="C33" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>319</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>320</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>147</v>
@@ -3111,7 +3111,7 @@
         <v>15</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>151</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="C34" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>316</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>317</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>147</v>
@@ -3184,7 +3184,7 @@
         <v>193</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>190</v>
@@ -3228,7 +3228,7 @@
         <v>196</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>197</v>
@@ -3272,7 +3272,7 @@
         <v>199</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>200</v>
@@ -3316,7 +3316,7 @@
         <v>204</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>205</v>
@@ -3360,7 +3360,7 @@
         <v>210</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>208</v>
@@ -3404,7 +3404,7 @@
         <v>214</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>212</v>
@@ -3448,7 +3448,7 @@
         <v>218</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>216</v>
@@ -3492,7 +3492,7 @@
         <v>226</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>220</v>
@@ -3536,7 +3536,7 @@
         <v>225</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>223</v>
@@ -3580,7 +3580,7 @@
         <v>228</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>229</v>
@@ -3624,7 +3624,7 @@
         <v>232</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>233</v>
@@ -3668,7 +3668,7 @@
         <v>236</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>237</v>
@@ -3712,7 +3712,7 @@
         <v>240</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>241</v>
@@ -3756,7 +3756,7 @@
         <v>244</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>245</v>
@@ -3800,7 +3800,7 @@
         <v>162</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>163</v>
@@ -3821,16 +3821,16 @@
         <v>56</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N49" s="2" t="s">
         <v>254</v>
@@ -3844,7 +3844,7 @@
         <v>66</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>103</v>
@@ -3865,16 +3865,16 @@
         <v>56</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N50" s="2" t="s">
         <v>254</v>
@@ -3888,13 +3888,13 @@
         <v>24</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D51" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>307</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>53</v>
@@ -3909,16 +3909,16 @@
         <v>152</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N51" s="2" t="s">
         <v>254</v>
@@ -3926,19 +3926,19 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="B52" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="D52" s="2" t="s">
+      <c r="E52" s="6" t="s">
         <v>339</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>340</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>53</v>
@@ -3947,7 +3947,7 @@
         <v>15</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>152</v>
@@ -3970,19 +3970,19 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B53" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="B53" s="5" t="s">
-        <v>353</v>
-      </c>
       <c r="C53" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>52</v>
@@ -3991,7 +3991,7 @@
         <v>15</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>151</v>
@@ -4003,7 +4003,7 @@
         <v>147</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="M53" s="2" t="s">
         <v>147</v>
@@ -4014,19 +4014,19 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B54" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="C54" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D54" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D54" s="2" t="s">
+      <c r="E54" s="6" t="s">
         <v>360</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>361</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>52</v>
@@ -4035,7 +4035,7 @@
         <v>15</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>56</v>
@@ -4058,19 +4058,19 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="B55" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="C55" s="2" t="s">
+      <c r="D55" t="s">
         <v>365</v>
       </c>
-      <c r="D55" t="s">
+      <c r="E55" s="6" t="s">
         <v>366</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>367</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>52</v>
@@ -4102,19 +4102,19 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B56" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D56" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="C56" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="D56" s="2" t="s">
+      <c r="E56" s="6" t="s">
         <v>375</v>
-      </c>
-      <c r="E56" s="6" t="s">
-        <v>376</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>150</v>
@@ -4152,7 +4152,7 @@
         <v>30</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>125</v>
@@ -4173,16 +4173,16 @@
         <v>56</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N57" s="2" t="s">
         <v>147</v>
@@ -4196,7 +4196,7 @@
         <v>31</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>115</v>
@@ -4223,10 +4223,10 @@
         <v>147</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="N58" s="2" t="s">
         <v>147</v>
@@ -4234,19 +4234,19 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B59" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="D59" t="s">
         <v>348</v>
       </c>
-      <c r="D59" t="s">
+      <c r="E59" s="6" t="s">
         <v>349</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>350</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>52</v>
@@ -4284,7 +4284,7 @@
         <v>32</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>126</v>
@@ -4305,16 +4305,16 @@
         <v>153</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>147</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="N60" s="2" t="s">
         <v>147</v>
@@ -4328,7 +4328,7 @@
         <v>33</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>118</v>
@@ -4355,10 +4355,10 @@
         <v>147</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="N61" s="2" t="s">
         <v>147</v>
@@ -4372,7 +4372,7 @@
         <v>34</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>127</v>
@@ -4393,16 +4393,16 @@
         <v>56</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L62" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M62" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="N62" s="2" t="s">
         <v>147</v>
@@ -4416,7 +4416,7 @@
         <v>35</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>121</v>
@@ -4446,7 +4446,7 @@
         <v>131</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="N63" s="2" t="s">
         <v>147</v>
@@ -4460,7 +4460,7 @@
         <v>39</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>136</v>
@@ -4481,16 +4481,16 @@
         <v>137</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="N64" s="2" t="s">
         <v>147</v>
@@ -4498,19 +4498,19 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D65" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="B65" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D65" s="2" t="s">
+      <c r="E65" s="6" t="s">
         <v>312</v>
-      </c>
-      <c r="E65" s="6" t="s">
-        <v>313</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>52</v>
@@ -4534,7 +4534,7 @@
         <v>131</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N65" s="2" t="s">
         <v>147</v>
@@ -4548,7 +4548,7 @@
         <v>180</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>182</v>
@@ -4569,16 +4569,16 @@
         <v>152</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N66" s="2" t="s">
         <v>254</v>
@@ -4592,7 +4592,7 @@
         <v>72</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>80</v>
@@ -4613,16 +4613,16 @@
         <v>152</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N67" s="2" t="s">
         <v>254</v>
@@ -4636,7 +4636,7 @@
         <v>247</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>186</v>
@@ -4657,16 +4657,16 @@
         <v>152</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N68" s="2" t="s">
         <v>254</v>
@@ -4674,19 +4674,19 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B69" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="B69" s="5" t="s">
+      <c r="C69" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D69" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="C69" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="D69" s="2" t="s">
+      <c r="E69" s="6" t="s">
         <v>380</v>
-      </c>
-      <c r="E69" s="6" t="s">
-        <v>381</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>52</v>
@@ -4701,10 +4701,10 @@
         <v>152</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>131</v>
@@ -4718,19 +4718,19 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="B70" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="C70" s="2" t="s">
+      <c r="D70" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="D70" s="2" t="s">
+      <c r="E70" s="5" t="s">
         <v>344</v>
-      </c>
-      <c r="E70" s="5" t="s">
-        <v>345</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>52</v>
@@ -4762,19 +4762,19 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B71" s="5" t="s">
         <v>394</v>
       </c>
-      <c r="B71" s="5" t="s">
+      <c r="C71" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="D71" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="C71" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="D71" s="2" t="s">
+      <c r="E71" s="6" t="s">
         <v>396</v>
-      </c>
-      <c r="E71" s="6" t="s">
-        <v>397</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>52</v>

--- a/files/Dashboards_Website.xlsx
+++ b/files/Dashboards_Website.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jschneid\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F7DFF1-FFE5-49EB-9D2F-01213F9CBAA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D21C993-A30E-4D15-AE97-61A674D50206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -803,16 +803,10 @@
     <t>OpenAIRE Monitor Dashboard</t>
   </si>
   <si>
-    <t>2013–2023</t>
-  </si>
-  <si>
     <t>2017–2024</t>
   </si>
   <si>
     <t>2006–2025</t>
-  </si>
-  <si>
-    <t>1976–2025</t>
   </si>
   <si>
     <t>2015–2024</t>
@@ -878,12 +872,6 @@
     <t>Licenses: bottom of page, sources: https://jugit.fz-juelich.de/synoa/oam-dokumentation/-/wikis/Quelldatenbanken/Quelldatenbanken</t>
   </si>
   <si>
-    <t>2005–2025</t>
-  </si>
-  <si>
-    <t>2014–2025</t>
-  </si>
-  <si>
     <t>2020–2024</t>
   </si>
   <si>
@@ -924,15 +912,6 @@
   </si>
   <si>
     <t>https://www.resources.osc.lmu.de/bibliography/</t>
-  </si>
-  <si>
-    <t>2017–2023</t>
-  </si>
-  <si>
-    <t>2016–2023</t>
-  </si>
-  <si>
-    <t>1990–2022</t>
   </si>
   <si>
     <t>2000–2025</t>
@@ -951,9 +930,6 @@
     <t>Austrian Transition to Open Access 2 (AT2OA²), Federal Ministry of Education, Science and Research (BMBWF)</t>
   </si>
   <si>
-    <t>2000–2024</t>
-  </si>
-  <si>
     <t>2007–2024</t>
   </si>
   <si>
@@ -1011,15 +987,9 @@
     <t>2007–2025</t>
   </si>
   <si>
-    <t>2008–2023</t>
-  </si>
-  <si>
     <t>2013–2024</t>
   </si>
   <si>
-    <t>2011–2024</t>
-  </si>
-  <si>
     <t>Open Access Monitor Austria</t>
   </si>
   <si>
@@ -1035,9 +1005,6 @@
     <t>https://europepmc.org/funder-dashboard?funderName=Academy%20of%20Medical%20Sciences&amp;tabName=Open%20Access</t>
   </si>
   <si>
-    <t>1913–2025</t>
-  </si>
-  <si>
     <t>Europe PMC</t>
   </si>
   <si>
@@ -1050,9 +1017,6 @@
     <t>https://monitor.openscience.si/</t>
   </si>
   <si>
-    <t>2010–2025</t>
-  </si>
-  <si>
     <t>Open Science Monitor</t>
   </si>
   <si>
@@ -1068,9 +1032,6 @@
     <t>Open Access an der Leibniz Universität Hannover</t>
   </si>
   <si>
-    <t>2019–2024</t>
-  </si>
-  <si>
     <t>Leibniz University Hannover</t>
   </si>
   <si>
@@ -1191,9 +1152,6 @@
     <t>https://lookerstudio.google.com/reporting/2b34c431-c3dd-4eed-ac69-0c8856bd8af7/page/GAiiF?utm_campaign=35281527-OSI-Dashboard&amp;utm_source=hubspot&amp;utm_medium=cta&amp;utm_content=explore-the-dashboard&amp;hsCtaAttrib=208961770045</t>
   </si>
   <si>
-    <t>2018–2024</t>
-  </si>
-  <si>
     <t>Public Library of Science (PLOS)</t>
   </si>
   <si>
@@ -1233,7 +1191,49 @@
     <t>https://ror.org/04n00c532</t>
   </si>
   <si>
-    <t>2006–2023</t>
+    <t>2005–2026</t>
+  </si>
+  <si>
+    <t>2017–2026</t>
+  </si>
+  <si>
+    <t>2006–2026</t>
+  </si>
+  <si>
+    <t>1976–2026</t>
+  </si>
+  <si>
+    <t>2015–2026</t>
+  </si>
+  <si>
+    <t>1913–2026</t>
+  </si>
+  <si>
+    <t>2007–2026</t>
+  </si>
+  <si>
+    <t>2008–2024</t>
+  </si>
+  <si>
+    <t>2011–2025</t>
+  </si>
+  <si>
+    <t>2014–2026</t>
+  </si>
+  <si>
+    <t>2020–2026</t>
+  </si>
+  <si>
+    <t>2013–2026</t>
+  </si>
+  <si>
+    <t>2010–2026</t>
+  </si>
+  <si>
+    <t>2018–2026</t>
+  </si>
+  <si>
+    <t>1990–2025</t>
   </si>
 </sst>
 </file>
@@ -1721,7 +1721,7 @@
         <v>251</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -1732,7 +1732,7 @@
         <v>59</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>255</v>
+        <v>315</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>84</v>
@@ -1753,13 +1753,13 @@
         <v>56</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="M2" s="5" t="s">
         <v>252</v>
@@ -1776,7 +1776,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>397</v>
+        <v>256</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>86</v>
@@ -1800,13 +1800,13 @@
         <v>147</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>154</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>147</v>
@@ -1820,7 +1820,7 @@
         <v>249</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>397</v>
+        <v>256</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>86</v>
@@ -1841,10 +1841,10 @@
         <v>56</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>131</v>
@@ -1864,7 +1864,7 @@
         <v>5</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>123</v>
@@ -1885,16 +1885,16 @@
         <v>56</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>147</v>
@@ -1908,7 +1908,7 @@
         <v>60</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>279</v>
+        <v>383</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>90</v>
@@ -1929,16 +1929,16 @@
         <v>56</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>147</v>
@@ -1946,19 +1946,19 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>381</v>
+        <v>368</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>383</v>
+        <v>351</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>150</v>
@@ -1976,13 +1976,13 @@
         <v>147</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>386</v>
+        <v>372</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>147</v>
@@ -1996,7 +1996,7 @@
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>283</v>
+        <v>384</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>91</v>
@@ -2017,16 +2017,16 @@
         <v>151</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="N8" s="4" t="s">
         <v>147</v>
@@ -2040,7 +2040,7 @@
         <v>134</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>257</v>
+        <v>385</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>133</v>
@@ -2061,16 +2061,16 @@
         <v>56</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>147</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>147</v>
@@ -2084,7 +2084,7 @@
         <v>63</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>258</v>
+        <v>386</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>155</v>
@@ -2128,7 +2128,7 @@
         <v>37</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>261</v>
+        <v>387</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>78</v>
@@ -2149,7 +2149,7 @@
         <v>56</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>147</v>
@@ -2158,7 +2158,7 @@
         <v>147</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>147</v>
@@ -2172,7 +2172,7 @@
         <v>58</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>79</v>
@@ -2196,13 +2196,13 @@
         <v>147</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>147</v>
@@ -2216,7 +2216,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>261</v>
+        <v>387</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>93</v>
@@ -2237,16 +2237,16 @@
         <v>129</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>147</v>
@@ -2260,7 +2260,7 @@
         <v>159</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>160</v>
@@ -2281,16 +2281,16 @@
         <v>153</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>254</v>
@@ -2304,7 +2304,7 @@
         <v>166</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>167</v>
@@ -2325,16 +2325,16 @@
         <v>153</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>254</v>
@@ -2348,7 +2348,7 @@
         <v>64</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>322</v>
+        <v>389</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>12</v>
@@ -2369,16 +2369,16 @@
         <v>152</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>254</v>
@@ -2392,7 +2392,7 @@
         <v>168</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>174</v>
@@ -2413,16 +2413,16 @@
         <v>153</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>254</v>
@@ -2436,7 +2436,7 @@
         <v>171</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>323</v>
+        <v>390</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>173</v>
@@ -2457,16 +2457,16 @@
         <v>172</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N18" s="2" t="s">
         <v>254</v>
@@ -2480,7 +2480,7 @@
         <v>177</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>178</v>
@@ -2501,16 +2501,16 @@
         <v>137</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>254</v>
@@ -2518,16 +2518,16 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>331</v>
+        <v>388</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>147</v>
@@ -2542,7 +2542,7 @@
         <v>10</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>147</v>
@@ -2554,7 +2554,7 @@
         <v>131</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>147</v>
@@ -2562,19 +2562,19 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>391</v>
+        <v>377</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>389</v>
+        <v>375</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>390</v>
+        <v>376</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>150</v>
@@ -2592,13 +2592,13 @@
         <v>147</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>392</v>
+        <v>378</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>147</v>
@@ -2612,7 +2612,7 @@
         <v>14</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>324</v>
+        <v>281</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>95</v>
@@ -2633,16 +2633,16 @@
         <v>152</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="N22" s="2" t="s">
         <v>147</v>
@@ -2650,19 +2650,19 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>53</v>
@@ -2677,10 +2677,10 @@
         <v>137</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>131</v>
@@ -2700,7 +2700,7 @@
         <v>17</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>279</v>
+        <v>383</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>97</v>
@@ -2724,13 +2724,13 @@
         <v>147</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="N24" s="2" t="s">
         <v>147</v>
@@ -2744,7 +2744,7 @@
         <v>19</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>99</v>
@@ -2762,19 +2762,19 @@
         <v>44</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>147</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="N25" s="2" t="s">
         <v>147</v>
@@ -2788,7 +2788,7 @@
         <v>21</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>261</v>
+        <v>387</v>
       </c>
       <c r="D26" t="s">
         <v>101</v>
@@ -2815,10 +2815,10 @@
         <v>147</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>147</v>
@@ -2832,7 +2832,7 @@
         <v>23</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>105</v>
@@ -2862,7 +2862,7 @@
         <v>147</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>147</v>
@@ -2920,7 +2920,7 @@
         <v>68</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>325</v>
+        <v>391</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>82</v>
@@ -2958,16 +2958,16 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>54</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>280</v>
+        <v>392</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>128</v>
@@ -2985,16 +2985,16 @@
         <v>56</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>147</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>147</v>
@@ -3008,7 +3008,7 @@
         <v>26</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>282</v>
+        <v>393</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>108</v>
@@ -3038,7 +3038,7 @@
         <v>131</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>147</v>
@@ -3052,7 +3052,7 @@
         <v>28</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>324</v>
+        <v>281</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>110</v>
@@ -3073,16 +3073,16 @@
         <v>56</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>147</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="N32" s="2" t="s">
         <v>147</v>
@@ -3090,16 +3090,16 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>327</v>
-      </c>
       <c r="D33" s="2" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>147</v>
@@ -3111,7 +3111,7 @@
         <v>15</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>151</v>
@@ -3134,16 +3134,16 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>147</v>
@@ -3184,7 +3184,7 @@
         <v>193</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>282</v>
+        <v>393</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>190</v>
@@ -3228,7 +3228,7 @@
         <v>196</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>283</v>
+        <v>384</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>197</v>
@@ -3272,7 +3272,7 @@
         <v>199</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>284</v>
+        <v>374</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>200</v>
@@ -3316,7 +3316,7 @@
         <v>204</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>280</v>
+        <v>392</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>205</v>
@@ -3360,7 +3360,7 @@
         <v>210</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>280</v>
+        <v>392</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>208</v>
@@ -3404,7 +3404,7 @@
         <v>214</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>261</v>
+        <v>387</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>212</v>
@@ -3448,7 +3448,7 @@
         <v>218</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>285</v>
+        <v>394</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>216</v>
@@ -3492,7 +3492,7 @@
         <v>226</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>283</v>
+        <v>384</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>220</v>
@@ -3536,7 +3536,7 @@
         <v>225</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>280</v>
+        <v>392</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>223</v>
@@ -3580,7 +3580,7 @@
         <v>228</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>280</v>
+        <v>392</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>229</v>
@@ -3624,7 +3624,7 @@
         <v>232</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>285</v>
+        <v>394</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>233</v>
@@ -3668,7 +3668,7 @@
         <v>236</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>285</v>
+        <v>394</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>237</v>
@@ -3712,7 +3712,7 @@
         <v>240</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>285</v>
+        <v>394</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>241</v>
@@ -3756,7 +3756,7 @@
         <v>244</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>261</v>
+        <v>387</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>245</v>
@@ -3800,7 +3800,7 @@
         <v>162</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>322</v>
+        <v>389</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>163</v>
@@ -3821,16 +3821,16 @@
         <v>56</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N49" s="2" t="s">
         <v>254</v>
@@ -3844,7 +3844,7 @@
         <v>66</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>103</v>
@@ -3865,16 +3865,16 @@
         <v>56</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N50" s="2" t="s">
         <v>254</v>
@@ -3888,13 +3888,13 @@
         <v>24</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>53</v>
@@ -3909,16 +3909,16 @@
         <v>152</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N51" s="2" t="s">
         <v>254</v>
@@ -3926,19 +3926,19 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>336</v>
+        <v>395</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>53</v>
@@ -3947,7 +3947,7 @@
         <v>15</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>152</v>
@@ -3970,19 +3970,19 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>52</v>
@@ -3991,7 +3991,7 @@
         <v>15</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>151</v>
@@ -4003,7 +4003,7 @@
         <v>147</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="M53" s="2" t="s">
         <v>147</v>
@@ -4014,19 +4014,19 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>52</v>
@@ -4035,7 +4035,7 @@
         <v>15</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>56</v>
@@ -4058,19 +4058,19 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>364</v>
+        <v>396</v>
       </c>
       <c r="D55" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>52</v>
@@ -4102,19 +4102,19 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>374</v>
+        <v>361</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>150</v>
@@ -4152,7 +4152,7 @@
         <v>30</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>125</v>
@@ -4173,16 +4173,16 @@
         <v>56</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="N57" s="2" t="s">
         <v>147</v>
@@ -4196,7 +4196,7 @@
         <v>31</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>325</v>
+        <v>391</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>115</v>
@@ -4223,10 +4223,10 @@
         <v>147</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="N58" s="2" t="s">
         <v>147</v>
@@ -4234,19 +4234,19 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="D59" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>52</v>
@@ -4284,7 +4284,7 @@
         <v>32</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>296</v>
+        <v>357</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>126</v>
@@ -4305,16 +4305,16 @@
         <v>153</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>147</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="N60" s="2" t="s">
         <v>147</v>
@@ -4328,7 +4328,7 @@
         <v>33</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>295</v>
+        <v>255</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>118</v>
@@ -4355,10 +4355,10 @@
         <v>147</v>
       </c>
       <c r="L61" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="M61" s="2" t="s">
         <v>289</v>
-      </c>
-      <c r="M61" s="2" t="s">
-        <v>293</v>
       </c>
       <c r="N61" s="2" t="s">
         <v>147</v>
@@ -4372,7 +4372,7 @@
         <v>34</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>296</v>
+        <v>357</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>127</v>
@@ -4393,16 +4393,16 @@
         <v>56</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L62" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M62" s="5" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="N62" s="2" t="s">
         <v>147</v>
@@ -4416,7 +4416,7 @@
         <v>35</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>297</v>
+        <v>397</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>121</v>
@@ -4446,7 +4446,7 @@
         <v>131</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="N63" s="2" t="s">
         <v>147</v>
@@ -4460,7 +4460,7 @@
         <v>39</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>136</v>
@@ -4481,16 +4481,16 @@
         <v>137</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="N64" s="2" t="s">
         <v>147</v>
@@ -4498,19 +4498,19 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>52</v>
@@ -4534,7 +4534,7 @@
         <v>131</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="N65" s="2" t="s">
         <v>147</v>
@@ -4548,7 +4548,7 @@
         <v>180</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>322</v>
+        <v>389</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>182</v>
@@ -4569,16 +4569,16 @@
         <v>152</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N66" s="2" t="s">
         <v>254</v>
@@ -4592,7 +4592,7 @@
         <v>72</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>80</v>
@@ -4613,16 +4613,16 @@
         <v>152</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N67" s="2" t="s">
         <v>254</v>
@@ -4636,7 +4636,7 @@
         <v>247</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>322</v>
+        <v>389</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>186</v>
@@ -4657,16 +4657,16 @@
         <v>152</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>131</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="N68" s="2" t="s">
         <v>254</v>
@@ -4674,19 +4674,19 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>322</v>
+        <v>389</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>52</v>
@@ -4701,10 +4701,10 @@
         <v>152</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>131</v>
@@ -4718,19 +4718,19 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>342</v>
+        <v>317</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>52</v>
@@ -4762,19 +4762,19 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>394</v>
+        <v>380</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>395</v>
+        <v>381</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>396</v>
+        <v>382</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>52</v>
